--- a/data/gravel/Sklar SuperSomething Ti 2025.xlsx
+++ b/data/gravel/Sklar SuperSomething Ti 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{242C8FE4-2DC6-3849-AE03-1076E3FD7124}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1042576C-EBB2-CF4C-86D4-C462BEB697D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9620" yWindow="2640" windowWidth="26340" windowHeight="14700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2460" yWindow="2640" windowWidth="26340" windowHeight="14700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="110">
   <si>
     <t>brand</t>
   </si>
@@ -360,6 +360,9 @@
   </si>
   <si>
     <t>USD</t>
+  </si>
+  <si>
+    <t>https://sklarbikes.com/cdn/shop/files/SKS02573-Edit.jpg?v=1757009837&amp;width=900</t>
   </si>
 </sst>
 </file>
@@ -744,6 +747,11 @@
         <v>8</v>
       </c>
     </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>109</v>
+      </c>
+    </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>9</v>

--- a/data/gravel/Sklar SuperSomething Ti 2025.xlsx
+++ b/data/gravel/Sklar SuperSomething Ti 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1042576C-EBB2-CF4C-86D4-C462BEB697D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED8DEED7-9678-DE46-8B8D-B26D814886C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2460" yWindow="2640" windowWidth="26340" windowHeight="14700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9520" yWindow="2340" windowWidth="26340" windowHeight="14700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="112">
   <si>
     <t>brand</t>
   </si>
@@ -363,6 +363,12 @@
   </si>
   <si>
     <t>https://sklarbikes.com/cdn/shop/files/SKS02573-Edit.jpg?v=1757009837&amp;width=900</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Oakland, California, USA</t>
   </si>
 </sst>
 </file>
@@ -701,7 +707,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G74"/>
+  <dimension ref="A1:G75"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1541,6 +1547,14 @@
         <v>108</v>
       </c>
     </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>110</v>
+      </c>
+      <c r="B75" t="s">
+        <v>111</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/data/gravel/Sklar SuperSomething Ti 2025.xlsx
+++ b/data/gravel/Sklar SuperSomething Ti 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED8DEED7-9678-DE46-8B8D-B26D814886C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA7511D4-FC49-8B4B-998E-ADE2E1771CB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9520" yWindow="2340" windowWidth="26340" windowHeight="14700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2460" yWindow="2340" windowWidth="26340" windowHeight="14700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="118">
   <si>
     <t>brand</t>
   </si>
@@ -369,6 +369,24 @@
   </si>
   <si>
     <t>Oakland, California, USA</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -707,7 +725,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G75"/>
+  <dimension ref="A1:G81"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1386,172 +1404,202 @@
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>69</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>70</v>
+        <v>113</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>71</v>
-      </c>
-      <c r="B53">
-        <v>27.2</v>
+        <v>114</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>72</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>95</v>
+        <v>115</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>73</v>
-      </c>
-      <c r="B55">
-        <v>44</v>
+        <v>116</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>74</v>
+        <v>117</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>75</v>
+        <v>69</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>77</v>
+        <v>71</v>
+      </c>
+      <c r="B59">
+        <v>27.2</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>79</v>
-      </c>
-      <c r="B61" s="1"/>
+        <v>73</v>
+      </c>
+      <c r="B61">
+        <v>44</v>
+      </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>82</v>
-      </c>
-      <c r="B64">
-        <v>2</v>
+        <v>76</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>83</v>
-      </c>
-      <c r="B65">
-        <v>1</v>
+        <v>77</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>85</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>93</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="B67" s="1"/>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>86</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>87</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>88</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>93</v>
+        <v>82</v>
+      </c>
+      <c r="B70">
+        <v>2</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="B71">
-        <v>2599</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>90</v>
+        <v>84</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>91</v>
+        <v>85</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>108</v>
+        <v>93</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
+        <v>87</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>88</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>89</v>
+      </c>
+      <c r="B77">
+        <v>2599</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>92</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
         <v>110</v>
       </c>
-      <c r="B75" t="s">
+      <c r="B81" t="s">
         <v>111</v>
       </c>
     </row>

--- a/data/gravel/Sklar SuperSomething Ti 2025.xlsx
+++ b/data/gravel/Sklar SuperSomething Ti 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA7511D4-FC49-8B4B-998E-ADE2E1771CB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{758C25DB-BE3C-0C40-B42B-C87EA66A97B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2460" yWindow="2340" windowWidth="26340" windowHeight="14700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -362,9 +362,6 @@
     <t>USD</t>
   </si>
   <si>
-    <t>https://sklarbikes.com/cdn/shop/files/SKS02573-Edit.jpg?v=1757009837&amp;width=900</t>
-  </si>
-  <si>
     <t>location</t>
   </si>
   <si>
@@ -387,6 +384,9 @@
   </si>
   <si>
     <t>fork_material</t>
+  </si>
+  <si>
+    <t>https://sklarbikes.com/cdn/shop/files/SKS02935_01d63ea7-f67a-4103-a184-4044a5db1810.jpg?v=1762382784&amp;width=720</t>
   </si>
 </sst>
 </file>
@@ -773,7 +773,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -1404,32 +1404,32 @@
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
@@ -1597,10 +1597,10 @@
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
+        <v>109</v>
+      </c>
+      <c r="B81" t="s">
         <v>110</v>
-      </c>
-      <c r="B81" t="s">
-        <v>111</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Sklar SuperSomething Ti 2025.xlsx
+++ b/data/gravel/Sklar SuperSomething Ti 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11109"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{758C25DB-BE3C-0C40-B42B-C87EA66A97B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D80C5F0-1BF3-A84A-A9F6-326E9A1CEF3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2460" yWindow="2340" windowWidth="26340" windowHeight="14700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="31400" yWindow="-17180" windowWidth="26340" windowHeight="14700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="119">
   <si>
     <t>brand</t>
   </si>
@@ -387,6 +387,9 @@
   </si>
   <si>
     <t>https://sklarbikes.com/cdn/shop/files/SKS02935_01d63ea7-f67a-4103-a184-4044a5db1810.jpg?v=1762382784&amp;width=720</t>
+  </si>
+  <si>
+    <t>delta</t>
   </si>
 </sst>
 </file>
@@ -725,13 +728,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G81"/>
+  <dimension ref="A1:L81"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -739,7 +742,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -747,7 +750,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -755,7 +758,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -763,7 +766,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -771,12 +774,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -784,7 +787,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -807,7 +810,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -830,7 +833,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -853,7 +856,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>20</v>
       </c>
@@ -875,8 +878,28 @@
       <c r="G11">
         <v>616</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H11">
+        <f>C10+C9/TAN(C15*PI()/180)</f>
+        <v>507.8439277644095</v>
+      </c>
+      <c r="I11">
+        <f t="shared" ref="I11:K11" si="0">D10+D9/TAN(D15*PI()/180)</f>
+        <v>539.17353503770312</v>
+      </c>
+      <c r="J11">
+        <f t="shared" si="0"/>
+        <v>565.80159144198262</v>
+      </c>
+      <c r="K11">
+        <f t="shared" si="0"/>
+        <v>590.54100736137593</v>
+      </c>
+      <c r="L11">
+        <f>G10+G9/TAN(G15*PI()/180)</f>
+        <v>616.50090667497284</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>22</v>
       </c>
@@ -898,8 +921,27 @@
       <c r="G12">
         <v>705</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H12" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="I12">
+        <f>I11-H11</f>
+        <v>31.329607273293618</v>
+      </c>
+      <c r="J12">
+        <f t="shared" ref="J12:L12" si="1">J11-I11</f>
+        <v>26.628056404279505</v>
+      </c>
+      <c r="K12">
+        <f t="shared" si="1"/>
+        <v>24.739415919393309</v>
+      </c>
+      <c r="L12">
+        <f t="shared" si="1"/>
+        <v>25.959899313596907</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>24</v>
       </c>
@@ -922,7 +964,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -945,7 +987,7 @@
         <v>70.5</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -968,7 +1010,7 @@
         <v>73.5</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>30</v>
       </c>
